--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.13181755704752</v>
+        <v>2.946420353020223</v>
       </c>
       <c r="D2" t="n">
-        <v>18.88643675960031</v>
+        <v>3.069045973435051</v>
       </c>
       <c r="E2" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F2" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.41216353757651</v>
+        <v>2.829476574856184</v>
       </c>
       <c r="D3" t="n">
-        <v>18.51540993385131</v>
+        <v>3.008754114250838</v>
       </c>
       <c r="E3" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F3" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.64166263472969</v>
+        <v>3.191770178143575</v>
       </c>
       <c r="D4" t="n">
-        <v>20.76205448537628</v>
+        <v>3.373833853873646</v>
       </c>
       <c r="E4" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F4" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.74547833992012</v>
+        <v>4.021140230237019</v>
       </c>
       <c r="D5" t="n">
-        <v>25.73290930503825</v>
+        <v>4.181597762068716</v>
       </c>
       <c r="E5" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F5" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.80188489399821</v>
+        <v>3.867806295274709</v>
       </c>
       <c r="D6" t="n">
-        <v>22.98325192077612</v>
+        <v>3.73477843712612</v>
       </c>
       <c r="E6" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F6" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.69650231730442</v>
+        <v>6.613181626561969</v>
       </c>
       <c r="D7" t="n">
-        <v>41.82539883726397</v>
+        <v>6.796627311055395</v>
       </c>
       <c r="E7" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F7" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.15966919809921</v>
+        <v>7.500946244691121</v>
       </c>
       <c r="D8" t="n">
-        <v>47.27877740991252</v>
+        <v>7.682801329110785</v>
       </c>
       <c r="E8" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F8" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>55.52167087424083</v>
+        <v>9.022271517064135</v>
       </c>
       <c r="D9" t="n">
-        <v>53.97310609733481</v>
+        <v>8.770629740816908</v>
       </c>
       <c r="E9" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F9" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.37238942529035</v>
+        <v>8.673013281609682</v>
       </c>
       <c r="D10" t="n">
-        <v>53.28944806337182</v>
+        <v>8.659535310297921</v>
       </c>
       <c r="E10" t="n">
-        <v>14.71665310893136</v>
+        <v>2.391456130201346</v>
       </c>
       <c r="F10" t="n">
-        <v>14.30181566929636</v>
+        <v>2.324045046260658</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
